--- a/data/basic_properties_data_coded.xlsx
+++ b/data/basic_properties_data_coded.xlsx
@@ -1,34 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofsussex-my.sharepoint.com/personal/acp29_sussex_ac_uk/Documents/Research/APOE/OGS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{554EF631-606D-E44F-8C71-430E587DE30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B92A290B-BCE3-3C4C-8579-02FCEEB6C4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1220" yWindow="-18820" windowWidth="27640" windowHeight="16160" xr2:uid="{A56CE306-5EFA-3C4B-B0BE-1572C5810D07}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27640" windowHeight="16160" xr2:uid="{194CA508-2263-D04E-A3D6-338AA1DDC583}"/>
   </bookViews>
   <sheets>
-    <sheet name="OGS" sheetId="1" r:id="rId1"/>
+    <sheet name="basic_properties_data_coded" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -83,10 +70,10 @@
     <t>sag</t>
   </si>
   <si>
-    <t>Apnum</t>
+    <t>maxApnum</t>
   </si>
   <si>
-    <t>maxApnum</t>
+    <t>RMP</t>
   </si>
   <si>
     <t>G1</t>
@@ -961,7 +948,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2925D4AD-95ED-4A4C-8756-79AB719E1ED7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9506FE5-8939-0040-BF27-C19FC5FCA81D}">
   <dimension ref="A1:R77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -1015,10 +1002,10 @@
         <v>15</v>
       </c>
       <c r="Q1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" t="s">
         <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -1044,7 +1031,7 @@
         <v>54.128617269999999</v>
       </c>
       <c r="H2">
-        <v>-8.5018755599999949</v>
+        <v>-48.280391029999997</v>
       </c>
       <c r="I2">
         <v>93.907132739999994</v>
@@ -1071,7 +1058,7 @@
         <v>15.5026376</v>
       </c>
       <c r="Q2">
-        <v>12</v>
+        <v>-62.703000000000003</v>
       </c>
       <c r="R2">
         <v>12</v>
@@ -1100,7 +1087,7 @@
         <v>48.681489030000002</v>
       </c>
       <c r="H3">
-        <v>-14.749465859999994</v>
+        <v>-52.664779099999997</v>
       </c>
       <c r="I3">
         <v>86.596802280000006</v>
@@ -1127,7 +1114,7 @@
         <v>29.40400876</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>-69.624600000000001</v>
       </c>
       <c r="R3">
         <v>3</v>
@@ -1156,7 +1143,7 @@
         <v>40.850857789999999</v>
       </c>
       <c r="H4">
-        <v>-11.078201119999996</v>
+        <v>-54.247811579999997</v>
       </c>
       <c r="I4">
         <v>84.020468260000001</v>
@@ -1183,7 +1170,7 @@
         <v>27.162468369999999</v>
       </c>
       <c r="Q4">
-        <v>8</v>
+        <v>-70.113600000000005</v>
       </c>
       <c r="R4">
         <v>14</v>
@@ -1212,7 +1199,7 @@
         <v>45.727825449999997</v>
       </c>
       <c r="H5">
-        <v>-9.3713851500000018</v>
+        <v>-51.560722689999999</v>
       </c>
       <c r="I5">
         <v>87.917163000000002</v>
@@ -1239,7 +1226,7 @@
         <v>23.97465759</v>
       </c>
       <c r="Q5">
-        <v>12</v>
+        <v>-68.756600000000006</v>
       </c>
       <c r="R5">
         <v>12</v>
@@ -1268,7 +1255,7 @@
         <v>53.939873319999997</v>
       </c>
       <c r="H6">
-        <v>-10.530732129999997</v>
+        <v>-47.98607071</v>
       </c>
       <c r="I6">
         <v>91.395211900000007</v>
@@ -1295,7 +1282,7 @@
         <v>19.508434399999999</v>
       </c>
       <c r="Q6">
-        <v>13</v>
+        <v>-71.278000000000006</v>
       </c>
       <c r="R6">
         <v>13</v>
@@ -1324,7 +1311,7 @@
         <v>69.626258649999997</v>
       </c>
       <c r="H7">
-        <v>-11.915510919999999</v>
+        <v>-24.441919819999999</v>
       </c>
       <c r="I7">
         <v>82.152667550000004</v>
@@ -1351,7 +1338,7 @@
         <v>-31.692461529999999</v>
       </c>
       <c r="Q7">
-        <v>13</v>
+        <v>-71.8001</v>
       </c>
       <c r="R7">
         <v>13</v>
@@ -1380,7 +1367,7 @@
         <v>47.30582673</v>
       </c>
       <c r="H8">
-        <v>-10.079875000000001</v>
+        <v>-48.855580660000001</v>
       </c>
       <c r="I8">
         <v>86.081532390000007</v>
@@ -1407,7 +1394,7 @@
         <v>25.535105269999999</v>
       </c>
       <c r="Q8">
-        <v>13</v>
+        <v>-65.706299999999999</v>
       </c>
       <c r="R8">
         <v>13</v>
@@ -1436,7 +1423,7 @@
         <v>44.950498369999998</v>
       </c>
       <c r="H9">
-        <v>-8.9914063999999954</v>
+        <v>-50.998608249999997</v>
       </c>
       <c r="I9">
         <v>86.957700220000007</v>
@@ -1463,7 +1450,7 @@
         <v>26.313658220000001</v>
       </c>
       <c r="Q9">
-        <v>11</v>
+        <v>-66.48</v>
       </c>
       <c r="R9">
         <v>11</v>
@@ -1492,7 +1479,7 @@
         <v>36.02020718</v>
       </c>
       <c r="H10">
-        <v>-8.3795215499999998</v>
+        <v>-47.800731200000001</v>
       </c>
       <c r="I10">
         <v>75.441416829999994</v>
@@ -1519,7 +1506,7 @@
         <v>25.416862819999999</v>
       </c>
       <c r="Q10">
-        <v>11</v>
+        <v>-65.745099999999994</v>
       </c>
       <c r="R10">
         <v>11</v>
@@ -1548,7 +1535,7 @@
         <v>35.969981660000002</v>
       </c>
       <c r="H11">
-        <v>-12.334160410000003</v>
+        <v>-47.406397400000003</v>
       </c>
       <c r="I11">
         <v>71.042218649999995</v>
@@ -1575,7 +1562,7 @@
         <v>24.603573669999999</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>-63.253799999999998</v>
       </c>
       <c r="R11">
         <v>5</v>
@@ -1604,7 +1591,7 @@
         <v>39.770065879999997</v>
       </c>
       <c r="H12">
-        <v>-13.4290989</v>
+        <v>-48.211499209999999</v>
       </c>
       <c r="I12">
         <v>74.552466179999996</v>
@@ -1631,7 +1618,7 @@
         <v>18.388710769999999</v>
       </c>
       <c r="Q12">
-        <v>10</v>
+        <v>-63.253799999999998</v>
       </c>
       <c r="R12">
         <v>10</v>
@@ -1660,7 +1647,7 @@
         <v>42.435328159999997</v>
       </c>
       <c r="H13">
-        <v>-11.483999250000004</v>
+        <v>-48.006838000000002</v>
       </c>
       <c r="I13">
         <v>78.958166910000003</v>
@@ -1687,7 +1674,7 @@
         <v>23.092097559999999</v>
       </c>
       <c r="Q13">
-        <v>14</v>
+        <v>-68.689300000000003</v>
       </c>
       <c r="R13">
         <v>14</v>
@@ -1716,7 +1703,7 @@
         <v>39.222596099999997</v>
       </c>
       <c r="H14">
-        <v>-9.6290179599999988</v>
+        <v>-48.823376590000002</v>
       </c>
       <c r="I14">
         <v>78.416954739999994</v>
@@ -1743,7 +1730,7 @@
         <v>29.44881552</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>-67.104399999999998</v>
       </c>
       <c r="R14">
         <v>8</v>
@@ -1772,7 +1759,7 @@
         <v>47.563459590000001</v>
       </c>
       <c r="H15">
-        <v>-8.1154265099999989</v>
+        <v>-47.921662560000001</v>
       </c>
       <c r="I15">
         <v>87.369695640000003</v>
@@ -1799,7 +1786,7 @@
         <v>23.606762069999998</v>
       </c>
       <c r="Q15">
-        <v>6</v>
+        <v>-70.1023</v>
       </c>
       <c r="R15">
         <v>9</v>
@@ -1828,7 +1815,7 @@
         <v>46.3719076</v>
       </c>
       <c r="H16">
-        <v>-11.40024202</v>
+        <v>-49.435253959999997</v>
       </c>
       <c r="I16">
         <v>84.406919540000004</v>
@@ -1855,7 +1842,7 @@
         <v>22.402494570000002</v>
       </c>
       <c r="Q16">
-        <v>11</v>
+        <v>-69.778499999999994</v>
       </c>
       <c r="R16">
         <v>11</v>
@@ -1884,7 +1871,7 @@
         <v>50.655054049999997</v>
       </c>
       <c r="H17">
-        <v>-8.7917121799999975</v>
+        <v>-46.601295589999999</v>
       </c>
       <c r="I17">
         <v>88.464637460000006</v>
@@ -1911,7 +1898,7 @@
         <v>19.819536549999999</v>
       </c>
       <c r="Q17">
-        <v>12</v>
+        <v>-70.701899999999995</v>
       </c>
       <c r="R17">
         <v>12</v>
@@ -1940,7 +1927,7 @@
         <v>42.990476389999998</v>
       </c>
       <c r="H18">
-        <v>-12.237548110000006</v>
+        <v>-48.114887000000003</v>
       </c>
       <c r="I18">
         <v>78.867815280000002</v>
@@ -1967,7 +1954,7 @@
         <v>26.027705359999999</v>
       </c>
       <c r="Q18">
-        <v>15</v>
+        <v>-61.522399999999998</v>
       </c>
       <c r="R18">
         <v>15</v>
@@ -1996,7 +1983,7 @@
         <v>45.234289410000002</v>
       </c>
       <c r="H19">
-        <v>-9.7578344500000043</v>
+        <v>-49.510139860000002</v>
       </c>
       <c r="I19">
         <v>84.986594819999993</v>
@@ -2023,7 +2010,7 @@
         <v>22.968439320000002</v>
       </c>
       <c r="Q19">
-        <v>8</v>
+        <v>-67.885800000000003</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -2052,7 +2039,7 @@
         <v>37.110309690000001</v>
       </c>
       <c r="H20">
-        <v>-9.6644678999999982</v>
+        <v>-58.925772240000001</v>
       </c>
       <c r="I20">
         <v>86.371614039999997</v>
@@ -2079,7 +2066,7 @@
         <v>24.881133930000001</v>
       </c>
       <c r="Q20">
-        <v>10</v>
+        <v>-65.255799999999994</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -2108,7 +2095,7 @@
         <v>41.141285279999998</v>
       </c>
       <c r="H21">
-        <v>-9.9220983599999997</v>
+        <v>-57.793222579999998</v>
       </c>
       <c r="I21">
         <v>89.012409500000004</v>
@@ -2135,7 +2122,7 @@
         <v>26.46332511</v>
       </c>
       <c r="Q21">
-        <v>7</v>
+        <v>-71.568299999999994</v>
       </c>
       <c r="R21">
         <v>8</v>
@@ -2164,7 +2151,7 @@
         <v>52.964938799999999</v>
       </c>
       <c r="H22">
-        <v>-7.9222023000000021</v>
+        <v>-46.191455810000001</v>
       </c>
       <c r="I22">
         <v>91.234192320000005</v>
@@ -2191,7 +2178,7 @@
         <v>20.869686009999999</v>
       </c>
       <c r="Q22">
-        <v>11</v>
+        <v>-65.7851</v>
       </c>
       <c r="R22">
         <v>11</v>
@@ -2220,7 +2207,7 @@
         <v>51.255635550000001</v>
       </c>
       <c r="H23">
-        <v>-6.2153863500000028</v>
+        <v>-45.292227029999999</v>
       </c>
       <c r="I23">
         <v>90.332476229999997</v>
@@ -2247,7 +2234,7 @@
         <v>22.492473799999999</v>
       </c>
       <c r="Q23">
-        <v>11</v>
+        <v>-30.255099999999999</v>
       </c>
       <c r="R23">
         <v>11</v>
@@ -2276,7 +2263,7 @@
         <v>50.334880579999997</v>
       </c>
       <c r="H24">
-        <v>-6.9882840600000051</v>
+        <v>-47.307919750000003</v>
       </c>
       <c r="I24">
         <v>90.654516270000002</v>
@@ -2303,7 +2290,7 @@
         <v>22.599710890000001</v>
       </c>
       <c r="Q24">
-        <v>8</v>
+        <v>-69.9709</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -2332,7 +2319,7 @@
         <v>40.985323289999997</v>
       </c>
       <c r="H25">
-        <v>-10.121760130000006</v>
+        <v>-49.347370920000003</v>
       </c>
       <c r="I25">
         <v>80.210934080000001</v>
@@ -2359,7 +2346,7 @@
         <v>21.877109740000002</v>
       </c>
       <c r="Q25">
-        <v>8</v>
+        <v>-71.581100000000006</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -2388,7 +2375,7 @@
         <v>50.709026540000004</v>
       </c>
       <c r="H26">
-        <v>-11.799599290000003</v>
+        <v>-48.599048580000002</v>
       </c>
       <c r="I26">
         <v>87.508475829999995</v>
@@ -2415,7 +2402,7 @@
         <v>23.17048248</v>
       </c>
       <c r="Q26">
-        <v>9</v>
+        <v>-71.415000000000006</v>
       </c>
       <c r="R26">
         <v>9</v>
@@ -2444,7 +2431,7 @@
         <v>41.469035220000002</v>
       </c>
       <c r="H27">
-        <v>-10.250579280000004</v>
+        <v>-57.027496910000004</v>
       </c>
       <c r="I27">
         <v>88.245952860000003</v>
@@ -2471,7 +2458,7 @@
         <v>23.467579279999999</v>
       </c>
       <c r="Q27">
-        <v>8</v>
+        <v>-65.895399999999995</v>
       </c>
       <c r="R27">
         <v>8</v>
@@ -2500,7 +2487,7 @@
         <v>39.995494610000002</v>
       </c>
       <c r="H28">
-        <v>-15.39354754</v>
+        <v>-48.404723650000001</v>
       </c>
       <c r="I28">
         <v>73.006670720000002</v>
@@ -2527,7 +2514,7 @@
         <v>21.136351350000002</v>
       </c>
       <c r="Q28">
-        <v>3</v>
+        <v>-68.467799999999997</v>
       </c>
       <c r="R28">
         <v>3</v>
@@ -2556,7 +2543,7 @@
         <v>47.692276020000001</v>
       </c>
       <c r="H29">
-        <v>-10.240895549999998</v>
+        <v>-46.79452002</v>
       </c>
       <c r="I29">
         <v>84.245900500000005</v>
@@ -2583,7 +2570,7 @@
         <v>20.380577240000001</v>
       </c>
       <c r="Q29">
-        <v>8</v>
+        <v>-70.602500000000006</v>
       </c>
       <c r="R29">
         <v>10</v>
@@ -2612,7 +2599,7 @@
         <v>37.416678900000001</v>
       </c>
       <c r="H30">
-        <v>-26.632772349999996</v>
+        <v>-44.252887549999997</v>
       </c>
       <c r="I30">
         <v>55.036794100000002</v>
@@ -2639,7 +2626,7 @@
         <v>15.13646935</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>-69.275800000000004</v>
       </c>
       <c r="R30">
         <v>2</v>
@@ -2668,7 +2655,7 @@
         <v>38.320881190000001</v>
       </c>
       <c r="H31">
-        <v>-16.520689969999999</v>
+        <v>-50.175947610000001</v>
       </c>
       <c r="I31">
         <v>71.976138840000004</v>
@@ -2695,7 +2682,7 @@
         <v>19.4222213</v>
       </c>
       <c r="Q31">
-        <v>4</v>
+        <v>-56.005200000000002</v>
       </c>
       <c r="R31">
         <v>4</v>
@@ -2724,7 +2711,7 @@
         <v>48.02674974</v>
       </c>
       <c r="H32">
-        <v>-8.5662834199999978</v>
+        <v>-51.870333039999998</v>
       </c>
       <c r="I32">
         <v>91.330799369999994</v>
@@ -2751,7 +2738,7 @@
         <v>24.95319194</v>
       </c>
       <c r="Q32">
-        <v>8</v>
+        <v>-62.988500000000002</v>
       </c>
       <c r="R32">
         <v>9</v>
@@ -2780,7 +2767,7 @@
         <v>41.412475219999997</v>
       </c>
       <c r="H33">
-        <v>-10.079875179999995</v>
+        <v>-46.665703729999997</v>
       </c>
       <c r="I33">
         <v>77.998303770000007</v>
@@ -2807,7 +2794,7 @@
         <v>19.767081579999999</v>
       </c>
       <c r="Q33">
-        <v>8</v>
+        <v>-66.311899999999994</v>
       </c>
       <c r="R33">
         <v>8</v>
@@ -2836,7 +2823,7 @@
         <v>39.931086399999998</v>
       </c>
       <c r="H34">
-        <v>-7.213712539999996</v>
+        <v>-46.214846719999997</v>
       </c>
       <c r="I34">
         <v>78.932220580000006</v>
@@ -2863,7 +2850,7 @@
         <v>21.127209090000001</v>
       </c>
       <c r="Q34">
-        <v>13</v>
+        <v>-66.709500000000006</v>
       </c>
       <c r="R34">
         <v>13</v>
@@ -2892,7 +2879,7 @@
         <v>44.117620109999997</v>
       </c>
       <c r="H35">
-        <v>-18.613954979999999</v>
+        <v>-49.982723180000001</v>
       </c>
       <c r="I35">
         <v>75.486388309999995</v>
@@ -2919,7 +2906,7 @@
         <v>20.597448289999999</v>
       </c>
       <c r="Q35">
-        <v>13</v>
+        <v>-69.905299999999997</v>
       </c>
       <c r="R35">
         <v>13</v>
@@ -2948,7 +2935,7 @@
         <v>37.601442769999998</v>
       </c>
       <c r="H36">
-        <v>-16.263099050000001</v>
+        <v>-51.443026420000002</v>
       </c>
       <c r="I36">
         <v>72.781370140000007</v>
@@ -2975,7 +2962,7 @@
         <v>9.4346593189999997</v>
       </c>
       <c r="Q36">
-        <v>3</v>
+        <v>-65.821100000000001</v>
       </c>
       <c r="R36">
         <v>3</v>
@@ -3004,7 +2991,7 @@
         <v>42.902292969999998</v>
       </c>
       <c r="H37">
-        <v>-16.082735869999997</v>
+        <v>-44.722012059999997</v>
       </c>
       <c r="I37">
         <v>71.541569159999995</v>
@@ -3031,7 +3018,7 @@
         <v>16.95848015</v>
       </c>
       <c r="Q37">
-        <v>13</v>
+        <v>-70.258499999999998</v>
       </c>
       <c r="R37">
         <v>13</v>
@@ -3060,7 +3047,7 @@
         <v>42.571823019999997</v>
       </c>
       <c r="H38">
-        <v>-8.2764471799999981</v>
+        <v>-43.735133079999997</v>
       </c>
       <c r="I38">
         <v>78.030508920000003</v>
@@ -3087,7 +3074,7 @@
         <v>19.501257989999999</v>
       </c>
       <c r="Q38">
-        <v>12</v>
+        <v>-66.424999999999997</v>
       </c>
       <c r="R38">
         <v>12</v>
@@ -3116,7 +3103,7 @@
         <v>44.343048860000003</v>
       </c>
       <c r="H39">
-        <v>-9.7900383300000016</v>
+        <v>-48.855580660000001</v>
       </c>
       <c r="I39">
         <v>83.408591189999996</v>
@@ -3143,7 +3130,7 @@
         <v>15.82761079</v>
       </c>
       <c r="Q39">
-        <v>7</v>
+        <v>-60.471800000000002</v>
       </c>
       <c r="R39">
         <v>7</v>
@@ -3172,7 +3159,7 @@
         <v>54.165302099999998</v>
       </c>
       <c r="H40">
-        <v>-10.723956659999999</v>
+        <v>-47.019948530000001</v>
       </c>
       <c r="I40">
         <v>90.46129397</v>
@@ -3199,7 +3186,7 @@
         <v>18.998862209999999</v>
       </c>
       <c r="Q40">
-        <v>16</v>
+        <v>-66.301299999999998</v>
       </c>
       <c r="R40">
         <v>16</v>
@@ -3228,7 +3215,7 @@
         <v>42.217577849999998</v>
       </c>
       <c r="H41">
-        <v>-13.074854260000002</v>
+        <v>-46.569091520000001</v>
       </c>
       <c r="I41">
         <v>75.711815110000003</v>
@@ -3255,7 +3242,7 @@
         <v>18.354173039999999</v>
       </c>
       <c r="Q41">
-        <v>11</v>
+        <v>-61.512700000000002</v>
       </c>
       <c r="R41">
         <v>13</v>
@@ -3284,7 +3271,7 @@
         <v>50.429625280000003</v>
       </c>
       <c r="H42">
-        <v>-8.1798347399999969</v>
+        <v>-46.923336319999997</v>
       </c>
       <c r="I42">
         <v>89.173126859999996</v>
@@ -3311,7 +3298,7 @@
         <v>16.796604729999999</v>
       </c>
       <c r="Q42">
-        <v>12</v>
+        <v>-62.595700000000001</v>
       </c>
       <c r="R42">
         <v>12</v>
@@ -3340,7 +3327,7 @@
         <v>33.303505870000002</v>
       </c>
       <c r="H43">
-        <v>-12.263333109999998</v>
+        <v>-55.57676515</v>
       </c>
       <c r="I43">
         <v>76.616937899999996</v>
@@ -3367,7 +3354,7 @@
         <v>20.551411519999998</v>
       </c>
       <c r="Q43">
-        <v>11</v>
+        <v>-64.331000000000003</v>
       </c>
       <c r="R43">
         <v>11</v>
@@ -3396,7 +3383,7 @@
         <v>46.511283069999998</v>
       </c>
       <c r="H44">
-        <v>-14.443551710000001</v>
+        <v>-50.210785090000002</v>
       </c>
       <c r="I44">
         <v>82.278516449999998</v>
@@ -3423,7 +3410,7 @@
         <v>17.991503309999999</v>
       </c>
       <c r="Q44">
-        <v>16</v>
+        <v>-70.878500000000003</v>
       </c>
       <c r="R44">
         <v>16</v>
@@ -3452,7 +3439,7 @@
         <v>46.511283069999998</v>
       </c>
       <c r="H45">
-        <v>-14.443551710000001</v>
+        <v>-50.210785090000002</v>
       </c>
       <c r="I45">
         <v>82.278516449999998</v>
@@ -3479,7 +3466,7 @@
         <v>17.991503309999999</v>
       </c>
       <c r="Q45">
-        <v>16</v>
+        <v>-66.218100000000007</v>
       </c>
       <c r="R45">
         <v>16</v>
@@ -3508,7 +3495,7 @@
         <v>33.945095340000002</v>
       </c>
       <c r="H46">
-        <v>-11.767402479999994</v>
+        <v>-62.590135009999997</v>
       </c>
       <c r="I46">
         <v>84.767827870000005</v>
@@ -3535,7 +3522,7 @@
         <v>27.754697329999999</v>
       </c>
       <c r="Q46">
-        <v>12</v>
+        <v>-66.258099999999999</v>
       </c>
       <c r="R46">
         <v>12</v>
@@ -3564,7 +3551,7 @@
         <v>49.100002600000003</v>
       </c>
       <c r="H47">
-        <v>-9.4035896600000015</v>
+        <v>-47.802102570000002</v>
       </c>
       <c r="I47">
         <v>87.498515510000004</v>
@@ -3591,7 +3578,7 @@
         <v>17.504462530000001</v>
       </c>
       <c r="Q47">
-        <v>12</v>
+        <v>-66.842200000000005</v>
       </c>
       <c r="R47">
         <v>12</v>
@@ -3620,7 +3607,7 @@
         <v>46.008863869999999</v>
       </c>
       <c r="H48">
-        <v>-9.5227660400000005</v>
+        <v>-51.882223230000001</v>
       </c>
       <c r="I48">
         <v>88.36832106</v>
@@ -3647,7 +3634,7 @@
         <v>22.292502639999999</v>
       </c>
       <c r="Q48">
-        <v>11</v>
+        <v>-63.619399999999999</v>
       </c>
       <c r="R48">
         <v>11</v>
@@ -3676,7 +3663,7 @@
         <v>45.66225438</v>
       </c>
       <c r="H49">
-        <v>-10.340752420000001</v>
+        <v>-56.763231990000001</v>
       </c>
       <c r="I49">
         <v>92.08473395</v>
@@ -3703,7 +3690,7 @@
         <v>19.923144369999999</v>
       </c>
       <c r="Q49">
-        <v>13</v>
+        <v>-69.344399999999993</v>
       </c>
       <c r="R49">
         <v>13</v>
@@ -3732,7 +3719,7 @@
         <v>42.346394279999998</v>
       </c>
       <c r="H50">
-        <v>-11.142609420000007</v>
+        <v>-49.467458030000003</v>
       </c>
       <c r="I50">
         <v>80.671242890000002</v>
@@ -3759,7 +3746,7 @@
         <v>22.15372601</v>
       </c>
       <c r="Q50">
-        <v>10</v>
+        <v>-67.2196</v>
       </c>
       <c r="R50">
         <v>11</v>
@@ -3788,7 +3775,7 @@
         <v>45.051539200000001</v>
       </c>
       <c r="H51">
-        <v>-10.015467040000004</v>
+        <v>-46.536887440000001</v>
       </c>
       <c r="I51">
         <v>81.572959600000004</v>
@@ -3815,7 +3802,7 @@
         <v>21.71717465</v>
       </c>
       <c r="Q51">
-        <v>11</v>
+        <v>-64.935000000000002</v>
       </c>
       <c r="R51">
         <v>11</v>
@@ -3844,7 +3831,7 @@
         <v>36.549655510000001</v>
       </c>
       <c r="H52">
-        <v>-15.329139609999995</v>
+        <v>-46.697907809999997</v>
       </c>
       <c r="I52">
         <v>67.918423709999999</v>
@@ -3871,7 +3858,7 @@
         <v>15.74474532</v>
       </c>
       <c r="Q52">
-        <v>6</v>
+        <v>-67.725999999999999</v>
       </c>
       <c r="R52">
         <v>8</v>
@@ -3900,7 +3887,7 @@
         <v>40.92941364</v>
       </c>
       <c r="H53">
-        <v>-13.139262599999999</v>
+        <v>-44.89447972</v>
       </c>
       <c r="I53">
         <v>72.684630769999998</v>
@@ -3927,7 +3914,7 @@
         <v>12.84238758</v>
       </c>
       <c r="Q53">
-        <v>7</v>
+        <v>-68.364900000000006</v>
       </c>
       <c r="R53">
         <v>7</v>
@@ -3956,7 +3943,7 @@
         <v>41.831128589999999</v>
       </c>
       <c r="H54">
-        <v>-11.239221970000003</v>
+        <v>-46.053826350000001</v>
       </c>
       <c r="I54">
         <v>76.645732969999997</v>
@@ -3983,7 +3970,7 @@
         <v>16.24295047</v>
       </c>
       <c r="Q54">
-        <v>7</v>
+        <v>-66.0732</v>
       </c>
       <c r="R54">
         <v>8</v>
@@ -4012,7 +3999,7 @@
         <v>44.61557157</v>
       </c>
       <c r="H55">
-        <v>-25.624833529999997</v>
+        <v>-52.789162949999998</v>
       </c>
       <c r="I55">
         <v>71.779900990000002</v>
@@ -4039,7 +4026,7 @@
         <v>17.59152169</v>
       </c>
       <c r="Q55">
-        <v>14</v>
+        <v>-58.6539</v>
       </c>
       <c r="R55">
         <v>14</v>
@@ -4068,7 +4055,7 @@
         <v>41.160031660000001</v>
       </c>
       <c r="H56">
-        <v>-24.822928680000004</v>
+        <v>-47.195292530000003</v>
       </c>
       <c r="I56">
         <v>63.5323955</v>
@@ -4095,7 +4082,7 @@
         <v>18.505823459999998</v>
       </c>
       <c r="Q56">
-        <v>13</v>
+        <v>-64.533799999999999</v>
       </c>
       <c r="R56">
         <v>13</v>
@@ -4124,7 +4111,7 @@
         <v>47.08039797</v>
       </c>
       <c r="H57">
-        <v>-12.881629570000001</v>
+        <v>-48.694560299999999</v>
       </c>
       <c r="I57">
         <v>82.893328699999998</v>
@@ -4151,7 +4138,7 @@
         <v>16.024645509999999</v>
       </c>
       <c r="Q57">
-        <v>12</v>
+        <v>-65.4649</v>
       </c>
       <c r="R57">
         <v>13</v>
@@ -4180,7 +4167,7 @@
         <v>43.28031335</v>
       </c>
       <c r="H58">
-        <v>-13.783343850000001</v>
+        <v>-47.309785189999999</v>
       </c>
       <c r="I58">
         <v>76.806754679999997</v>
@@ -4207,7 +4194,7 @@
         <v>18.28521581</v>
       </c>
       <c r="Q58">
-        <v>14</v>
+        <v>-64.411000000000001</v>
       </c>
       <c r="R58">
         <v>14</v>
@@ -4236,7 +4223,7 @@
         <v>45.599009019999997</v>
       </c>
       <c r="H59">
-        <v>-10.788364789999996</v>
+        <v>-47.341989259999998</v>
       </c>
       <c r="I59">
         <v>82.152633499999993</v>
@@ -4263,7 +4250,7 @@
         <v>18.8286166</v>
       </c>
       <c r="Q59">
-        <v>14</v>
+        <v>-63.414400000000001</v>
       </c>
       <c r="R59">
         <v>14</v>
@@ -4292,7 +4279,7 @@
         <v>45.148151519999999</v>
       </c>
       <c r="H60">
-        <v>-10.691752299999997</v>
+        <v>-50.304763899999998</v>
       </c>
       <c r="I60">
         <v>84.76116313</v>
@@ -4319,7 +4306,7 @@
         <v>17.7778834</v>
       </c>
       <c r="Q60">
-        <v>12</v>
+        <v>-66.996200000000002</v>
       </c>
       <c r="R60">
         <v>12</v>
@@ -4348,7 +4335,7 @@
         <v>45.40578438</v>
       </c>
       <c r="H61">
-        <v>-10.756160900000005</v>
+        <v>-45.280928600000003</v>
       </c>
       <c r="I61">
         <v>79.930552079999998</v>
@@ -4375,7 +4362,7 @@
         <v>18.056906059999999</v>
       </c>
       <c r="Q61">
-        <v>13</v>
+        <v>-64.602999999999994</v>
       </c>
       <c r="R61">
         <v>14</v>
@@ -4404,7 +4391,7 @@
         <v>47.66007192</v>
       </c>
       <c r="H62">
-        <v>-14.685057929999999</v>
+        <v>-47.792846269999998</v>
       </c>
       <c r="I62">
         <v>80.767860260000006</v>
@@ -4431,7 +4418,7 @@
         <v>16.99820828</v>
       </c>
       <c r="Q62">
-        <v>12</v>
+        <v>-62.686799999999998</v>
       </c>
       <c r="R62">
         <v>12</v>
@@ -4460,7 +4447,7 @@
         <v>43.859987259999997</v>
       </c>
       <c r="H63">
-        <v>-11.432446560000002</v>
+        <v>-44.669051209999999</v>
       </c>
       <c r="I63">
         <v>77.096591910000001</v>
@@ -4487,7 +4474,7 @@
         <v>16.66981844</v>
       </c>
       <c r="Q63">
-        <v>9</v>
+        <v>-61.860999999999997</v>
       </c>
       <c r="R63">
         <v>10</v>
@@ -4516,7 +4503,7 @@
         <v>42.8322571</v>
       </c>
       <c r="H64">
-        <v>-12.14093621</v>
+        <v>-52.008786110000003</v>
       </c>
       <c r="I64">
         <v>82.700107009999996</v>
@@ -4543,7 +4530,7 @@
         <v>18.60597945</v>
       </c>
       <c r="Q64">
-        <v>10</v>
+        <v>-65.244799999999998</v>
       </c>
       <c r="R64">
         <v>10</v>
@@ -4572,7 +4559,7 @@
         <v>44.40745707</v>
       </c>
       <c r="H65">
-        <v>-9.7900385499999985</v>
+        <v>-46.08603042</v>
       </c>
       <c r="I65">
         <v>80.703448940000001</v>
@@ -4599,7 +4586,7 @@
         <v>18.42742939</v>
       </c>
       <c r="Q65">
-        <v>11</v>
+        <v>-64.206000000000003</v>
       </c>
       <c r="R65">
         <v>11</v>
@@ -4628,7 +4615,7 @@
         <v>45.921050100000002</v>
       </c>
       <c r="H66">
-        <v>-11.207017879999995</v>
+        <v>-46.150438569999999</v>
       </c>
       <c r="I66">
         <v>80.864470780000005</v>
@@ -4655,7 +4642,7 @@
         <v>10.77874991</v>
       </c>
       <c r="Q66">
-        <v>9</v>
+        <v>-58.994100000000003</v>
       </c>
       <c r="R66">
         <v>9</v>
@@ -4684,7 +4671,7 @@
         <v>44.214232430000003</v>
       </c>
       <c r="H67">
-        <v>-8.7595080900000042</v>
+        <v>-46.762315950000001</v>
       </c>
       <c r="I67">
         <v>82.21704029</v>
@@ -4711,7 +4698,7 @@
         <v>16.463450699999999</v>
       </c>
       <c r="Q67">
-        <v>9</v>
+        <v>-65.262299999999996</v>
       </c>
       <c r="R67">
         <v>9</v>
@@ -4740,7 +4727,7 @@
         <v>50.139788289999998</v>
       </c>
       <c r="H68">
-        <v>-11.947711570000003</v>
+        <v>-46.730111880000003</v>
       </c>
       <c r="I68">
         <v>84.922188599999998</v>
@@ -4767,7 +4754,7 @@
         <v>17.746399069999999</v>
       </c>
       <c r="Q68">
-        <v>12</v>
+        <v>-63.913699999999999</v>
       </c>
       <c r="R68">
         <v>12</v>
@@ -4796,7 +4783,7 @@
         <v>44.922722780000001</v>
       </c>
       <c r="H69">
-        <v>-14.588445870000005</v>
+        <v>-46.472479300000003</v>
       </c>
       <c r="I69">
         <v>76.806756210000003</v>
@@ -4823,7 +4810,7 @@
         <v>14.063916470000001</v>
       </c>
       <c r="Q69">
-        <v>13</v>
+        <v>-59.2971</v>
       </c>
       <c r="R69">
         <v>13</v>
@@ -4852,7 +4839,7 @@
         <v>47.144806189999997</v>
       </c>
       <c r="H70">
-        <v>-16.037628980000001</v>
+        <v>-49.016601020000003</v>
       </c>
       <c r="I70">
         <v>80.123778220000005</v>
@@ -4879,7 +4866,7 @@
         <v>16.553594270000001</v>
       </c>
       <c r="Q70">
-        <v>16</v>
+        <v>-61.628999999999998</v>
       </c>
       <c r="R70">
         <v>16</v>
@@ -4908,7 +4895,7 @@
         <v>44.085416000000002</v>
       </c>
       <c r="H71">
-        <v>-12.913833419999996</v>
+        <v>-50.755620899999997</v>
       </c>
       <c r="I71">
         <v>81.927203489999997</v>
@@ -4935,7 +4922,7 @@
         <v>18.933711450000001</v>
       </c>
       <c r="Q71">
-        <v>16</v>
+        <v>-65.682599999999994</v>
       </c>
       <c r="R71">
         <v>16</v>
@@ -4964,7 +4951,7 @@
         <v>48.400766410000003</v>
       </c>
       <c r="H72">
-        <v>-15.039302540000001</v>
+        <v>-49.596274319999999</v>
       </c>
       <c r="I72">
         <v>82.957738180000007</v>
@@ -4991,7 +4978,7 @@
         <v>13.48786853</v>
       </c>
       <c r="Q72">
-        <v>14</v>
+        <v>-61.463700000000003</v>
       </c>
       <c r="R72">
         <v>14</v>
@@ -5020,7 +5007,7 @@
         <v>46.854969220000001</v>
       </c>
       <c r="H73">
-        <v>-12.462976380000001</v>
+        <v>-50.626804620000001</v>
       </c>
       <c r="I73">
         <v>85.018797449999994</v>
@@ -5047,7 +5034,7 @@
         <v>14.366452750000001</v>
       </c>
       <c r="Q73">
-        <v>15</v>
+        <v>-62.885399999999997</v>
       </c>
       <c r="R73">
         <v>15</v>
@@ -5076,7 +5063,7 @@
         <v>43.602354409999997</v>
       </c>
       <c r="H74">
-        <v>-12.462976669999996</v>
+        <v>-47.857254419999997</v>
       </c>
       <c r="I74">
         <v>78.996632160000004</v>
@@ -5103,7 +5090,7 @@
         <v>19.988280939999999</v>
       </c>
       <c r="Q74">
-        <v>6</v>
+        <v>-65.763099999999994</v>
       </c>
       <c r="R74">
         <v>6</v>
@@ -5132,7 +5119,7 @@
         <v>44.439661170000001</v>
       </c>
       <c r="H75">
-        <v>-13.525711120000004</v>
+        <v>-48.340315500000003</v>
       </c>
       <c r="I75">
         <v>79.254265559999993</v>
@@ -5159,7 +5146,7 @@
         <v>19.103145520000002</v>
       </c>
       <c r="Q75">
-        <v>13</v>
+        <v>-62.763100000000001</v>
       </c>
       <c r="R75">
         <v>13</v>
@@ -5188,7 +5175,7 @@
         <v>45.40578438</v>
       </c>
       <c r="H76">
-        <v>-13.042650010000003</v>
+        <v>-48.114887000000003</v>
       </c>
       <c r="I76">
         <v>80.478021369999993</v>
@@ -5215,7 +5202,7 @@
         <v>17.110353440000001</v>
       </c>
       <c r="Q76">
-        <v>13</v>
+        <v>-62.109000000000002</v>
       </c>
       <c r="R76">
         <v>13</v>
@@ -5244,7 +5231,7 @@
         <v>46.790560999999997</v>
       </c>
       <c r="H77">
-        <v>-11.625670569999997</v>
+        <v>-49.177621379999998</v>
       </c>
       <c r="I77">
         <v>84.342511810000005</v>
@@ -5271,7 +5258,7 @@
         <v>20.61862356</v>
       </c>
       <c r="Q77">
-        <v>11</v>
+        <v>-67.415199999999999</v>
       </c>
       <c r="R77">
         <v>11</v>

--- a/data/basic_properties_data_coded.xlsx
+++ b/data/basic_properties_data_coded.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofsussex-my.sharepoint.com/personal/acp29_sussex_ac_uk/Documents/Research/APOE/OGS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B92A290B-BCE3-3C4C-8579-02FCEEB6C4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{972BA743-8909-4147-9EE8-6956CB05830B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27640" windowHeight="16160" xr2:uid="{194CA508-2263-D04E-A3D6-338AA1DDC583}"/>
+    <workbookView xWindow="1220" yWindow="920" windowWidth="27640" windowHeight="16160" xr2:uid="{194CA508-2263-D04E-A3D6-338AA1DDC583}"/>
   </bookViews>
   <sheets>
-    <sheet name="basic_properties_data_coded" sheetId="1" r:id="rId1"/>
+    <sheet name="OGS" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
